--- a/Result/profitability/9933.xlsx
+++ b/Result/profitability/9933.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5575</v>
+        <v>0.71125</v>
       </c>
       <c r="N2" t="n">
-        <v>9.190000000000001</v>
+        <v>10.215</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5625</v>
+        <v>0.6975</v>
       </c>
       <c r="N3" t="n">
-        <v>9.21125</v>
+        <v>10.17375</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0.56625</v>
+        <v>0.96875</v>
       </c>
       <c r="N4" t="n">
-        <v>9.328750000000001</v>
+        <v>9.63625</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.84375</v>
+        <v>1.01625</v>
       </c>
       <c r="N5" t="n">
-        <v>8.622499999999999</v>
+        <v>9.373749999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0.885</v>
+        <v>0.9912500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>8.647500000000001</v>
+        <v>9.196249999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8337500000000001</v>
+        <v>0.7787499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.390000000000001</v>
+        <v>8.5175</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.69875</v>
+        <v>0.78625</v>
       </c>
       <c r="N8" t="n">
-        <v>8.112500000000001</v>
+        <v>8.190000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.52</v>
       </c>
       <c r="M9" t="n">
-        <v>0.63875</v>
+        <v>0.6387499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>7.2275</v>
@@ -1645,10 +1645,10 @@
         <v>0.37</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6125</v>
+        <v>0.6124999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>7.30375</v>
+        <v>7.303749999999999</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0.82</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="N12" t="n">
         <v>7.89625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9933</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>20521</v>
+      </c>
+      <c r="D75" t="n">
+        <v>17717</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2804</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2297</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.20%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>290</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2587</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1566</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.870000000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6199999999999992</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04750957854406135</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.3125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.7845953002610966</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
